--- a/python-maps/documentation/CDA2FHIR_elga_eImpf_groups.xlsx
+++ b/python-maps/documentation/CDA2FHIR_elga_eImpf_groups.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DND_GIT_Repos\02_HL7Austria\hl7at_gh_CDA2FHIR\python-maps\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DND_Git_Repos\02_HL7Austria\hl7at_gh_CDA2FHIR\python-maps\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E4C39E-F025-4AC8-8025-E16A1EFCA2C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34DB0462-7927-4ED8-AA1D-160BB8141BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Header_Komplett_Imm" sheetId="6" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Entries" sheetId="3" r:id="rId3"/>
     <sheet name="Misc" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191028" refMode="R1C1"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="920" uniqueCount="345">
   <si>
     <t>CDA</t>
   </si>
@@ -2178,7 +2178,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2324,6 +2324,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2773,27 +2776,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49405C3E-CC40-4843-B308-4B97C855C16B}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.453125" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.81640625" style="21" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="47.54296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="50.26953125" style="21" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="0.453125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" style="21" customWidth="1"/>
-    <col min="9" max="9" width="29.54296875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="0.453125" style="22" customWidth="1"/>
-    <col min="11" max="11" width="42.26953125" style="21" customWidth="1"/>
-    <col min="12" max="12" width="21.453125" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="58.26953125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="50.28515625" style="21" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="0.42578125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" style="21" customWidth="1"/>
+    <col min="9" max="9" width="29.5703125" style="21" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="42.28515625" style="21" customWidth="1"/>
+    <col min="12" max="12" width="21.42578125" style="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="58.28515625" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="25" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="22" customWidth="1"/>
-    <col min="16" max="16384" width="8.7265625" style="45"/>
+    <col min="15" max="15" width="0.42578125" style="22" customWidth="1"/>
+    <col min="16" max="16384" width="8.7109375" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="53" t="s">
         <v>0</v>
@@ -2821,7 +2824,7 @@
       <c r="S1" s="44"/>
       <c r="T1" s="44"/>
     </row>
-    <row r="2" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
@@ -2867,7 +2870,7 @@
       <c r="S2" s="46"/>
       <c r="T2" s="46"/>
     </row>
-    <row r="3" spans="1:20" s="48" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" s="48" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -2897,7 +2900,7 @@
       <c r="S3" s="47"/>
       <c r="T3" s="47"/>
     </row>
-    <row r="4" spans="1:20" s="50" customFormat="1" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" s="50" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>13</v>
       </c>
@@ -2933,7 +2936,7 @@
       <c r="S4" s="49"/>
       <c r="T4" s="49"/>
     </row>
-    <row r="5" spans="1:20" s="50" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" s="50" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>13</v>
       </c>
@@ -2967,7 +2970,7 @@
       <c r="S5" s="49"/>
       <c r="T5" s="49"/>
     </row>
-    <row r="6" spans="1:20" s="48" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" s="48" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>23</v>
       </c>
@@ -2999,7 +3002,7 @@
       <c r="S6" s="47"/>
       <c r="T6" s="47"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="8"/>
       <c r="C7" s="2"/>
@@ -3016,7 +3019,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="51"/>
     </row>
-    <row r="8" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>13</v>
       </c>
@@ -3046,7 +3049,7 @@
       <c r="S8" s="47"/>
       <c r="T8" s="47"/>
     </row>
-    <row r="9" spans="1:20" ht="116" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="120" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -3071,7 +3074,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="51"/>
     </row>
-    <row r="10" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -3096,7 +3099,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="51"/>
     </row>
-    <row r="11" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -3126,7 +3129,7 @@
       <c r="S11" s="47"/>
       <c r="T11" s="47"/>
     </row>
-    <row r="12" spans="1:20" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -3150,7 +3153,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="51"/>
     </row>
-    <row r="13" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -3177,7 +3180,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="51"/>
     </row>
-    <row r="14" spans="1:20" s="48" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" s="48" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>30</v>
       </c>
@@ -3207,7 +3210,7 @@
       <c r="S14" s="47"/>
       <c r="T14" s="47"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="8"/>
       <c r="C15" s="2"/>
@@ -3222,7 +3225,7 @@
       <c r="L15" s="2"/>
       <c r="O15" s="51"/>
     </row>
-    <row r="16" spans="1:20" s="48" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" s="48" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>13</v>
       </c>
@@ -3254,7 +3257,7 @@
       <c r="S16" s="47"/>
       <c r="T16" s="47"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="8"/>
       <c r="C17" s="2"/>
@@ -3271,7 +3274,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="51"/>
     </row>
-    <row r="18" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>30</v>
       </c>
@@ -3301,7 +3304,7 @@
       <c r="S18" s="47"/>
       <c r="T18" s="47"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="8"/>
       <c r="C19" s="2"/>
@@ -3316,7 +3319,7 @@
       <c r="L19" s="2"/>
       <c r="O19" s="51"/>
     </row>
-    <row r="20" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>30</v>
       </c>
@@ -3346,7 +3349,7 @@
       <c r="S20" s="47"/>
       <c r="T20" s="47"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="8"/>
       <c r="C21" s="2"/>
@@ -3361,7 +3364,7 @@
       <c r="L21" s="2"/>
       <c r="O21" s="51"/>
     </row>
-    <row r="22" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -3391,7 +3394,7 @@
       <c r="S22" s="47"/>
       <c r="T22" s="47"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="8"/>
       <c r="C23" s="2"/>
@@ -3406,7 +3409,7 @@
       <c r="L23" s="2"/>
       <c r="O23" s="51"/>
     </row>
-    <row r="24" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>30</v>
       </c>
@@ -3436,7 +3439,7 @@
       <c r="S24" s="47"/>
       <c r="T24" s="47"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="8"/>
       <c r="C25" s="2"/>
@@ -3451,7 +3454,7 @@
       <c r="L25" s="2"/>
       <c r="O25" s="51"/>
     </row>
-    <row r="26" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>30</v>
       </c>
@@ -3481,7 +3484,7 @@
       <c r="S26" s="47"/>
       <c r="T26" s="47"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="8"/>
       <c r="C27" s="2"/>
@@ -3496,7 +3499,7 @@
       <c r="L27" s="2"/>
       <c r="O27" s="51"/>
     </row>
-    <row r="28" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>13</v>
       </c>
@@ -3528,7 +3531,7 @@
       <c r="S28" s="47"/>
       <c r="T28" s="47"/>
     </row>
-    <row r="29" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -3557,7 +3560,7 @@
       </c>
       <c r="O29" s="51"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>13</v>
       </c>
@@ -3582,7 +3585,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="51"/>
     </row>
-    <row r="31" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>30</v>
       </c>
@@ -3605,7 +3608,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="51"/>
     </row>
-    <row r="32" spans="1:20" s="48" customFormat="1" ht="58" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" s="48" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>13</v>
       </c>
@@ -3639,7 +3642,7 @@
       <c r="S32" s="47"/>
       <c r="T32" s="47"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="8"/>
       <c r="C33" s="2"/>
@@ -3656,7 +3659,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="51"/>
     </row>
-    <row r="34" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>30</v>
       </c>
@@ -3686,7 +3689,7 @@
       <c r="S34" s="47"/>
       <c r="T34" s="47"/>
     </row>
-    <row r="36" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>30</v>
       </c>
@@ -3746,26 +3749,26 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE723959-9FB8-4D0B-B907-ECADE5AE84A1}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="21"/>
-    <col min="2" max="2" width="45.453125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" style="21"/>
+    <col min="2" max="2" width="45.42578125" style="21" customWidth="1"/>
     <col min="3" max="3" width="10" style="21" customWidth="1"/>
-    <col min="4" max="4" width="49.54296875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="22.54296875" style="21" customWidth="1"/>
-    <col min="6" max="6" width="42.54296875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="0.453125" style="22" customWidth="1"/>
-    <col min="8" max="9" width="29.1796875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="0.453125" style="22" customWidth="1"/>
-    <col min="11" max="11" width="56.453125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="49.5703125" style="21" customWidth="1"/>
+    <col min="5" max="5" width="22.5703125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="42.5703125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="0.42578125" style="22" customWidth="1"/>
+    <col min="8" max="9" width="29.140625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="56.42578125" style="21" customWidth="1"/>
     <col min="12" max="12" width="14" style="21" customWidth="1"/>
-    <col min="13" max="13" width="42.81640625" style="21" customWidth="1"/>
-    <col min="14" max="14" width="46.81640625" style="21" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="22" customWidth="1"/>
-    <col min="16" max="16384" width="10.81640625" style="10"/>
+    <col min="13" max="13" width="42.85546875" style="21" customWidth="1"/>
+    <col min="14" max="14" width="46.85546875" style="21" customWidth="1"/>
+    <col min="15" max="15" width="0.42578125" style="22" customWidth="1"/>
+    <col min="16" max="16384" width="10.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="52" t="s">
         <v>0</v>
@@ -3793,7 +3796,7 @@
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
     </row>
-    <row r="2" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>73</v>
       </c>
@@ -3834,7 +3837,7 @@
       </c>
       <c r="O2" s="12"/>
     </row>
-    <row r="3" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
@@ -3864,7 +3867,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>30</v>
       </c>
@@ -3885,7 +3888,7 @@
       <c r="L4" s="25"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>30</v>
       </c>
@@ -3906,7 +3909,7 @@
       <c r="L5" s="25"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>30</v>
       </c>
@@ -3929,7 +3932,7 @@
       <c r="L6" s="25"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>30</v>
       </c>
@@ -3952,7 +3955,7 @@
       <c r="L7" s="25"/>
       <c r="O7" s="51"/>
     </row>
-    <row r="8" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
@@ -3975,7 +3978,7 @@
       <c r="L8" s="25"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
         <v>30</v>
       </c>
@@ -3998,7 +4001,7 @@
       <c r="L9" s="25"/>
       <c r="O9" s="51"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -4025,7 +4028,7 @@
       <c r="L10" s="25"/>
       <c r="O10" s="51"/>
     </row>
-    <row r="11" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
@@ -4048,7 +4051,7 @@
       <c r="L11" s="25"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -4071,7 +4074,7 @@
       <c r="L12" s="25"/>
       <c r="O12" s="51"/>
     </row>
-    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>23</v>
       </c>
@@ -4099,7 +4102,7 @@
       <c r="M13" s="27"/>
       <c r="O13" s="51"/>
     </row>
-    <row r="14" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -4124,7 +4127,7 @@
       <c r="L14" s="25"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>30</v>
       </c>
@@ -4147,7 +4150,7 @@
       <c r="J15" s="51"/>
       <c r="O15" s="51"/>
     </row>
-    <row r="16" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
@@ -4177,7 +4180,7 @@
       <c r="S16" s="6"/>
       <c r="T16" s="6"/>
     </row>
-    <row r="17" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
         <v>30</v>
       </c>
@@ -4198,7 +4201,7 @@
       <c r="L17" s="2"/>
       <c r="O17" s="51"/>
     </row>
-    <row r="18" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
@@ -4219,7 +4222,7 @@
       <c r="L18" s="25"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
         <v>30</v>
       </c>
@@ -4242,7 +4245,7 @@
       <c r="L19" s="25"/>
       <c r="O19" s="51"/>
     </row>
-    <row r="20" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="24" t="s">
         <v>30</v>
       </c>
@@ -4265,7 +4268,7 @@
       <c r="L20" s="25"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>30</v>
       </c>
@@ -4288,7 +4291,7 @@
       <c r="L21" s="25"/>
       <c r="O21" s="51"/>
     </row>
-    <row r="22" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4311,7 +4314,7 @@
       <c r="L22" s="2"/>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -4338,7 +4341,7 @@
       <c r="L23" s="2"/>
       <c r="O23" s="51"/>
     </row>
-    <row r="24" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>13</v>
       </c>
@@ -4361,7 +4364,7 @@
       <c r="L24" s="2"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -4384,7 +4387,7 @@
       <c r="L25" s="2"/>
       <c r="O25" s="51"/>
     </row>
-    <row r="26" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -4412,7 +4415,7 @@
       <c r="M26" s="27"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>30</v>
       </c>
@@ -4437,42 +4440,42 @@
       <c r="L27" s="2"/>
       <c r="O27" s="51"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="J28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G29" s="51"/>
       <c r="J29" s="51"/>
       <c r="O29" s="51"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G30" s="51"/>
       <c r="J30" s="51"/>
       <c r="O30" s="51"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G31" s="51"/>
       <c r="J31" s="51"/>
       <c r="O31" s="51"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G32" s="5"/>
       <c r="J32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="51"/>
       <c r="J33" s="51"/>
       <c r="O33" s="51"/>
     </row>
-    <row r="34" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G34" s="5"/>
       <c r="J34" s="5"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="36" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G36" s="5"/>
       <c r="J36" s="5"/>
       <c r="O36" s="5"/>
@@ -4504,27 +4507,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3618EA3D-690C-461F-8FC4-A0061C002499}">
   <dimension ref="A1:T140"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="21"/>
+    <col min="1" max="1" width="10.85546875" style="21"/>
     <col min="2" max="2" width="43" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.81640625" style="21"/>
-    <col min="4" max="4" width="60.1796875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="21"/>
+    <col min="4" max="4" width="60.140625" style="21" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" style="21" customWidth="1"/>
     <col min="6" max="6" width="19" style="21" customWidth="1"/>
-    <col min="7" max="7" width="0.453125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="29.81640625" style="25" customWidth="1"/>
-    <col min="9" max="9" width="23.1796875" style="25" customWidth="1"/>
-    <col min="10" max="10" width="0.453125" style="22" customWidth="1"/>
-    <col min="11" max="11" width="62.1796875" style="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.81640625" style="21" customWidth="1"/>
-    <col min="13" max="13" width="36.81640625" style="21" customWidth="1"/>
-    <col min="14" max="14" width="36.54296875" style="21" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="22" customWidth="1"/>
-    <col min="16" max="16384" width="10.81640625" style="10"/>
+    <col min="7" max="7" width="0.42578125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="29.85546875" style="25" customWidth="1"/>
+    <col min="9" max="9" width="23.140625" style="25" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="62.140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" style="21" customWidth="1"/>
+    <col min="13" max="13" width="36.85546875" style="21" customWidth="1"/>
+    <col min="14" max="14" width="36.5703125" style="21" customWidth="1"/>
+    <col min="15" max="15" width="0.42578125" style="22" customWidth="1"/>
+    <col min="16" max="16384" width="10.85546875" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="52" t="s">
         <v>0</v>
@@ -4552,7 +4555,7 @@
       <c r="S1" s="9"/>
       <c r="T1" s="9"/>
     </row>
-    <row r="2" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
         <v>3</v>
       </c>
@@ -4593,7 +4596,7 @@
       </c>
       <c r="O2" s="12"/>
     </row>
-    <row r="3" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
@@ -4623,7 +4626,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
         <v>30</v>
       </c>
@@ -4646,7 +4649,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>30</v>
       </c>
@@ -4669,7 +4672,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>30</v>
       </c>
@@ -4692,7 +4695,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>30</v>
       </c>
@@ -4717,7 +4720,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="51"/>
     </row>
-    <row r="8" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
         <v>30</v>
       </c>
@@ -4742,7 +4745,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
         <v>30</v>
       </c>
@@ -4767,7 +4770,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="51"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -4792,7 +4795,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="51"/>
     </row>
-    <row r="11" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>30</v>
       </c>
@@ -4817,7 +4820,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:20" ht="116" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>30</v>
       </c>
@@ -4842,7 +4845,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="51"/>
     </row>
-    <row r="13" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -4875,7 +4878,7 @@
       </c>
       <c r="O13" s="51"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
@@ -4900,7 +4903,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="5"/>
     </row>
-    <row r="15" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -4935,7 +4938,7 @@
       </c>
       <c r="O15" s="51"/>
     </row>
-    <row r="16" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
@@ -4960,7 +4963,7 @@
       <c r="N16" s="2"/>
       <c r="O16" s="5"/>
     </row>
-    <row r="17" spans="1:15" ht="145" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" ht="180" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>13</v>
       </c>
@@ -4987,7 +4990,7 @@
       <c r="N17" s="2"/>
       <c r="O17" s="51"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>13</v>
       </c>
@@ -5014,7 +5017,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="5"/>
     </row>
-    <row r="19" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
@@ -5043,7 +5046,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="51"/>
     </row>
-    <row r="20" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -5070,7 +5073,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="5"/>
     </row>
-    <row r="21" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>13</v>
       </c>
@@ -5097,7 +5100,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="51"/>
     </row>
-    <row r="22" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -5124,7 +5127,7 @@
       <c r="N22" s="2"/>
       <c r="O22" s="5"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>13</v>
       </c>
@@ -5151,7 +5154,7 @@
       <c r="N23" s="2"/>
       <c r="O23" s="51"/>
     </row>
-    <row r="24" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -5180,7 +5183,7 @@
       <c r="N24" s="2"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:15" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>13</v>
       </c>
@@ -5209,7 +5212,7 @@
       <c r="N25" s="2"/>
       <c r="O25" s="51"/>
     </row>
-    <row r="26" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
@@ -5238,7 +5241,7 @@
       <c r="N26" s="2"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
         <v>13</v>
       </c>
@@ -5265,7 +5268,7 @@
       <c r="N27" s="2"/>
       <c r="O27" s="51"/>
     </row>
-    <row r="28" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="24" t="s">
         <v>30</v>
       </c>
@@ -5292,7 +5295,7 @@
       <c r="N28" s="2"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>13</v>
       </c>
@@ -5321,7 +5324,7 @@
       <c r="N29" s="2"/>
       <c r="O29" s="51"/>
     </row>
-    <row r="30" spans="1:15" ht="58" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="24" t="s">
         <v>13</v>
       </c>
@@ -5350,7 +5353,7 @@
       <c r="N30" s="2"/>
       <c r="O30" s="51"/>
     </row>
-    <row r="31" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
         <v>30</v>
       </c>
@@ -5376,7 +5379,7 @@
       <c r="N31" s="2"/>
       <c r="O31" s="51"/>
     </row>
-    <row r="32" spans="1:15" ht="87" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="90" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>13</v>
       </c>
@@ -5405,7 +5408,7 @@
       <c r="N32" s="2"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>13</v>
       </c>
@@ -5432,7 +5435,7 @@
       <c r="N33" s="2"/>
       <c r="O33" s="51"/>
     </row>
-    <row r="34" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>30</v>
       </c>
@@ -5459,7 +5462,7 @@
       <c r="N34" s="2"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="35" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>13</v>
       </c>
@@ -5483,7 +5486,7 @@
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
     </row>
-    <row r="36" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>13</v>
       </c>
@@ -5510,7 +5513,7 @@
       <c r="N36" s="2"/>
       <c r="O36" s="5"/>
     </row>
-    <row r="37" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>13</v>
       </c>
@@ -5534,7 +5537,7 @@
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
     </row>
-    <row r="38" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>23</v>
       </c>
@@ -5562,7 +5565,7 @@
       <c r="S38" s="6"/>
       <c r="T38" s="6"/>
     </row>
-    <row r="39" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
         <v>30</v>
       </c>
@@ -5582,7 +5585,7 @@
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
     </row>
-    <row r="40" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
         <v>30</v>
       </c>
@@ -5604,7 +5607,7 @@
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
     </row>
-    <row r="41" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="24" t="s">
         <v>30</v>
       </c>
@@ -5626,7 +5629,7 @@
       <c r="M41" s="2"/>
       <c r="N41" s="2"/>
     </row>
-    <row r="42" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="24" t="s">
         <v>30</v>
       </c>
@@ -5648,7 +5651,7 @@
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
     </row>
-    <row r="43" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A43" s="24" t="s">
         <v>85</v>
       </c>
@@ -5672,7 +5675,7 @@
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
     </row>
-    <row r="44" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>30</v>
       </c>
@@ -5694,7 +5697,7 @@
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
     </row>
-    <row r="45" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>30</v>
       </c>
@@ -5714,7 +5717,7 @@
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
     </row>
-    <row r="46" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>30</v>
       </c>
@@ -5734,7 +5737,7 @@
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
     </row>
-    <row r="47" spans="1:20" ht="145" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" ht="165" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>13</v>
       </c>
@@ -5764,7 +5767,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>30</v>
       </c>
@@ -5784,7 +5787,7 @@
       <c r="M48" s="32"/>
       <c r="N48" s="32"/>
     </row>
-    <row r="49" spans="1:20" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:20" ht="225" x14ac:dyDescent="0.25">
       <c r="A49" s="24" t="s">
         <v>30</v>
       </c>
@@ -5805,7 +5808,7 @@
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
     </row>
-    <row r="50" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>13</v>
       </c>
@@ -5827,7 +5830,7 @@
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
     </row>
-    <row r="51" spans="1:20" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:20" ht="225" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>30</v>
       </c>
@@ -5849,7 +5852,7 @@
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
     </row>
-    <row r="52" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>23</v>
       </c>
@@ -5875,7 +5878,7 @@
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
     </row>
-    <row r="53" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>13</v>
       </c>
@@ -5903,7 +5906,7 @@
       <c r="S53" s="6"/>
       <c r="T53" s="6"/>
     </row>
-    <row r="54" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="24" t="s">
         <v>30</v>
       </c>
@@ -5923,7 +5926,7 @@
       <c r="M54" s="2"/>
       <c r="N54" s="2"/>
     </row>
-    <row r="55" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="24" t="s">
         <v>30</v>
       </c>
@@ -5934,7 +5937,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="56" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
         <v>30</v>
       </c>
@@ -5954,7 +5957,7 @@
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
     </row>
-    <row r="57" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
         <v>30</v>
       </c>
@@ -5976,7 +5979,7 @@
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
     </row>
-    <row r="58" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>13</v>
       </c>
@@ -6008,7 +6011,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="59" spans="1:20" ht="116" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>30</v>
       </c>
@@ -6030,7 +6033,7 @@
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
     </row>
-    <row r="60" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="24" t="s">
         <v>30</v>
       </c>
@@ -6052,7 +6055,7 @@
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
     </row>
-    <row r="61" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>13</v>
       </c>
@@ -6080,7 +6083,7 @@
       <c r="S61" s="6"/>
       <c r="T61" s="6"/>
     </row>
-    <row r="62" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="24" t="s">
         <v>30</v>
       </c>
@@ -6100,7 +6103,7 @@
       <c r="M62" s="2"/>
       <c r="N62" s="2"/>
     </row>
-    <row r="63" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="24" t="s">
         <v>30</v>
       </c>
@@ -6120,7 +6123,7 @@
       <c r="M63" s="2"/>
       <c r="N63" s="2"/>
     </row>
-    <row r="64" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="24" t="s">
         <v>30</v>
       </c>
@@ -6140,7 +6143,7 @@
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
     </row>
-    <row r="65" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>30</v>
       </c>
@@ -6162,7 +6165,7 @@
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
     </row>
-    <row r="66" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>30</v>
       </c>
@@ -6188,7 +6191,7 @@
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
     </row>
-    <row r="67" spans="1:20" ht="116" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>30</v>
       </c>
@@ -6210,7 +6213,7 @@
       <c r="M67" s="2"/>
       <c r="N67" s="2"/>
     </row>
-    <row r="68" spans="1:20" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>13</v>
       </c>
@@ -6221,8 +6224,12 @@
       <c r="D68" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="35"/>
+      <c r="E68" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="F68" s="35" t="s">
+        <v>211</v>
+      </c>
       <c r="H68" s="2" t="s">
         <v>215</v>
       </c>
@@ -6234,7 +6241,7 @@
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
     </row>
-    <row r="69" spans="1:20" s="7" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>13</v>
       </c>
@@ -6264,7 +6271,7 @@
       <c r="S69" s="6"/>
       <c r="T69" s="6"/>
     </row>
-    <row r="70" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="24" t="s">
         <v>30</v>
       </c>
@@ -6284,7 +6291,7 @@
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
     </row>
-    <row r="71" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="24" t="s">
         <v>30</v>
       </c>
@@ -6304,7 +6311,7 @@
       <c r="M71" s="2"/>
       <c r="N71" s="2"/>
     </row>
-    <row r="72" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="24" t="s">
         <v>30</v>
       </c>
@@ -6322,7 +6329,7 @@
       <c r="L72" s="8"/>
       <c r="N72" s="2"/>
     </row>
-    <row r="73" spans="1:20" ht="145" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:20" ht="165" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>13</v>
       </c>
@@ -6350,7 +6357,7 @@
       <c r="M73" s="2"/>
       <c r="N73" s="2"/>
     </row>
-    <row r="74" spans="1:20" ht="116" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>30</v>
       </c>
@@ -6372,7 +6379,7 @@
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
     </row>
-    <row r="75" spans="1:20" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:20" ht="315" x14ac:dyDescent="0.25">
       <c r="A75" s="24" t="s">
         <v>13</v>
       </c>
@@ -6398,7 +6405,7 @@
       <c r="M75" s="2"/>
       <c r="N75" s="2"/>
     </row>
-    <row r="76" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>23</v>
       </c>
@@ -6426,7 +6433,7 @@
       <c r="S76" s="6"/>
       <c r="T76" s="6"/>
     </row>
-    <row r="77" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="24" t="s">
         <v>30</v>
       </c>
@@ -6446,7 +6453,7 @@
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
     </row>
-    <row r="78" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
         <v>30</v>
       </c>
@@ -6466,7 +6473,7 @@
       <c r="M78" s="2"/>
       <c r="N78" s="2"/>
     </row>
-    <row r="79" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="24" t="s">
         <v>13</v>
       </c>
@@ -6488,7 +6495,7 @@
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
     </row>
-    <row r="80" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="24" t="s">
         <v>30</v>
       </c>
@@ -6510,7 +6517,7 @@
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
     </row>
-    <row r="81" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="24" t="s">
         <v>30</v>
       </c>
@@ -6532,7 +6539,7 @@
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
     </row>
-    <row r="82" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="24" t="s">
         <v>30</v>
       </c>
@@ -6554,7 +6561,7 @@
       <c r="M82" s="2"/>
       <c r="N82" s="2"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="24" t="s">
         <v>13</v>
       </c>
@@ -6576,7 +6583,7 @@
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="24" t="s">
         <v>13</v>
       </c>
@@ -6598,7 +6605,7 @@
       <c r="M84" s="2"/>
       <c r="N84" s="2"/>
     </row>
-    <row r="85" spans="1:14" ht="116" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" ht="135" x14ac:dyDescent="0.25">
       <c r="A85" s="24" t="s">
         <v>30</v>
       </c>
@@ -6620,7 +6627,7 @@
       <c r="M85" s="2"/>
       <c r="N85" s="2"/>
     </row>
-    <row r="86" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="24" t="s">
         <v>30</v>
       </c>
@@ -6642,7 +6649,7 @@
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
     </row>
-    <row r="87" spans="1:14" ht="145" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A87" s="24" t="s">
         <v>13</v>
       </c>
@@ -6666,7 +6673,7 @@
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
     </row>
-    <row r="88" spans="1:14" ht="145" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A88" s="24" t="s">
         <v>13</v>
       </c>
@@ -6690,7 +6697,7 @@
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
     </row>
-    <row r="89" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="24" t="s">
         <v>30</v>
       </c>
@@ -6712,7 +6719,7 @@
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
     </row>
-    <row r="90" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="24" t="s">
         <v>30</v>
       </c>
@@ -6734,7 +6741,7 @@
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
     </row>
-    <row r="91" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="24" t="s">
         <v>13</v>
       </c>
@@ -6756,7 +6763,7 @@
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
     </row>
-    <row r="92" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>23</v>
       </c>
@@ -6782,7 +6789,7 @@
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
     </row>
-    <row r="93" spans="1:14" ht="174" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" ht="180" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>13</v>
       </c>
@@ -6806,7 +6813,7 @@
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
     </row>
-    <row r="94" spans="1:14" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" ht="105" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>13</v>
       </c>
@@ -6832,7 +6839,7 @@
       <c r="M94" s="32"/>
       <c r="N94" s="2"/>
     </row>
-    <row r="95" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>13</v>
       </c>
@@ -6858,7 +6865,7 @@
       <c r="M95" s="32"/>
       <c r="N95" s="2"/>
     </row>
-    <row r="96" spans="1:14" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="24" t="s">
         <v>13</v>
       </c>
@@ -6882,7 +6889,7 @@
       <c r="M96" s="32"/>
       <c r="N96" s="2"/>
     </row>
-    <row r="97" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="24" t="s">
         <v>13</v>
       </c>
@@ -6908,7 +6915,7 @@
       <c r="M97" s="2"/>
       <c r="N97" s="2"/>
     </row>
-    <row r="98" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
         <v>30</v>
       </c>
@@ -6931,7 +6938,7 @@
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
     </row>
-    <row r="99" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>13</v>
       </c>
@@ -6957,7 +6964,7 @@
       <c r="M99" s="32"/>
       <c r="N99" s="2"/>
     </row>
-    <row r="100" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>13</v>
       </c>
@@ -6981,7 +6988,7 @@
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
     </row>
-    <row r="101" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>13</v>
       </c>
@@ -7005,7 +7012,7 @@
       <c r="M101" s="2"/>
       <c r="N101" s="2"/>
     </row>
-    <row r="102" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>30</v>
       </c>
@@ -7029,7 +7036,7 @@
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
     </row>
-    <row r="103" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>13</v>
       </c>
@@ -7053,7 +7060,7 @@
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
     </row>
-    <row r="104" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>13</v>
       </c>
@@ -7077,7 +7084,7 @@
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
     </row>
-    <row r="105" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:20" s="7" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
         <v>23</v>
       </c>
@@ -7105,7 +7112,7 @@
       <c r="S105" s="6"/>
       <c r="T105" s="6"/>
     </row>
-    <row r="106" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="24" t="s">
         <v>30</v>
       </c>
@@ -7125,7 +7132,7 @@
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
     </row>
-    <row r="107" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="24" t="s">
         <v>30</v>
       </c>
@@ -7147,7 +7154,7 @@
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
     </row>
-    <row r="108" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="24" t="s">
         <v>30</v>
       </c>
@@ -7169,7 +7176,7 @@
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
     </row>
-    <row r="109" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="24" t="s">
         <v>30</v>
       </c>
@@ -7191,7 +7198,7 @@
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
     </row>
-    <row r="110" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A110" s="24" t="s">
         <v>85</v>
       </c>
@@ -7215,7 +7222,7 @@
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
     </row>
-    <row r="111" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>30</v>
       </c>
@@ -7235,7 +7242,7 @@
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
     </row>
-    <row r="112" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>30</v>
       </c>
@@ -7255,7 +7262,7 @@
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
     </row>
-    <row r="113" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>30</v>
       </c>
@@ -7275,7 +7282,7 @@
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
     </row>
-    <row r="114" spans="1:20" ht="145" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:20" ht="165" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>13</v>
       </c>
@@ -7301,7 +7308,7 @@
       <c r="M114" s="25"/>
       <c r="N114" s="25"/>
     </row>
-    <row r="115" spans="1:20" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>30</v>
       </c>
@@ -7321,7 +7328,7 @@
       <c r="M115" s="32"/>
       <c r="N115" s="32"/>
     </row>
-    <row r="116" spans="1:20" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:20" ht="225" x14ac:dyDescent="0.25">
       <c r="A116" s="24" t="s">
         <v>30</v>
       </c>
@@ -7342,7 +7349,7 @@
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
     </row>
-    <row r="117" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>30</v>
       </c>
@@ -7364,7 +7371,7 @@
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
     </row>
-    <row r="118" spans="1:20" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:20" ht="225" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>30</v>
       </c>
@@ -7386,7 +7393,7 @@
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
     </row>
-    <row r="119" spans="1:20" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:20" ht="225" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>30</v>
       </c>
@@ -7410,7 +7417,7 @@
       <c r="M119" s="2"/>
       <c r="N119" s="2"/>
     </row>
-    <row r="120" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
         <v>13</v>
       </c>
@@ -7438,7 +7445,7 @@
       <c r="S120" s="6"/>
       <c r="T120" s="6"/>
     </row>
-    <row r="121" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="24" t="s">
         <v>30</v>
       </c>
@@ -7449,7 +7456,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="122" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="24" t="s">
         <v>30</v>
       </c>
@@ -7460,7 +7467,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="123" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="24" t="s">
         <v>30</v>
       </c>
@@ -7474,7 +7481,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="124" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="24" t="s">
         <v>30</v>
       </c>
@@ -7488,7 +7495,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="125" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="24" t="s">
         <v>30</v>
       </c>
@@ -7502,7 +7509,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="126" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="24" t="s">
         <v>30</v>
       </c>
@@ -7513,7 +7520,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="127" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A127" s="24" t="s">
         <v>30</v>
       </c>
@@ -7527,7 +7534,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="128" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A128" s="24" t="s">
         <v>13</v>
       </c>
@@ -7544,7 +7551,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="129" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="24" t="s">
         <v>30</v>
       </c>
@@ -7558,7 +7565,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="130" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="24" t="s">
         <v>30</v>
       </c>
@@ -7572,7 +7579,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="131" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="24" t="s">
         <v>30</v>
       </c>
@@ -7586,7 +7593,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="132" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:20" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
         <v>13</v>
       </c>
@@ -7614,7 +7621,7 @@
       <c r="S132" s="6"/>
       <c r="T132" s="6"/>
     </row>
-    <row r="133" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="24" t="s">
         <v>30</v>
       </c>
@@ -7625,7 +7632,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="134" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="24" t="s">
         <v>30</v>
       </c>
@@ -7636,7 +7643,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="135" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="24" t="s">
         <v>30</v>
       </c>
@@ -7647,7 +7654,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="136" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A136" s="24" t="s">
         <v>13</v>
       </c>
@@ -7661,7 +7668,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="137" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="24" t="s">
         <v>13</v>
       </c>
@@ -7675,7 +7682,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="24" t="s">
         <v>30</v>
       </c>
@@ -7689,7 +7696,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="139" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A139" s="24" t="s">
         <v>30</v>
       </c>
@@ -7703,7 +7710,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="140" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:20" ht="135" x14ac:dyDescent="0.25">
       <c r="A140" s="24" t="s">
         <v>30</v>
       </c>
@@ -7756,34 +7763,35 @@
     <hyperlink ref="E75" r:id="rId16" xr:uid="{C9287547-2E5F-42AB-B58F-352776F27DCE}"/>
     <hyperlink ref="F75" r:id="rId17" xr:uid="{79E5DBD6-5497-4831-9AA1-97C2254A0F37}"/>
     <hyperlink ref="D76" r:id="rId18" xr:uid="{D9B59C76-A36A-439D-973C-7F89C9DB119A}"/>
+    <hyperlink ref="E68" r:id="rId19" xr:uid="{7B7D79BD-EEED-4381-83C9-702173AF72FA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId19"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId20"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEA87127-0BF5-4A9C-B8AD-0804EAFADC68}">
   <dimension ref="A1:T36"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" style="21" customWidth="1"/>
-    <col min="3" max="3" width="13.54296875" style="21" customWidth="1"/>
-    <col min="4" max="4" width="56.1796875" style="21" customWidth="1"/>
-    <col min="5" max="5" width="29.54296875" style="21" customWidth="1"/>
-    <col min="6" max="6" width="32.1796875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="0.453125" style="22" customWidth="1"/>
-    <col min="8" max="9" width="33.1796875" style="21" customWidth="1"/>
-    <col min="10" max="10" width="0.453125" style="22" customWidth="1"/>
-    <col min="11" max="11" width="49.81640625" style="21" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" style="21" customWidth="1"/>
-    <col min="13" max="14" width="49.81640625" style="21" customWidth="1"/>
-    <col min="15" max="15" width="0.453125" style="22" customWidth="1"/>
-    <col min="16" max="16384" width="12.54296875" style="45"/>
+    <col min="1" max="1" width="9.5703125" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="21" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="56.140625" style="21" customWidth="1"/>
+    <col min="5" max="5" width="29.5703125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" style="21" customWidth="1"/>
+    <col min="7" max="7" width="0.42578125" style="22" customWidth="1"/>
+    <col min="8" max="9" width="33.140625" style="21" customWidth="1"/>
+    <col min="10" max="10" width="0.42578125" style="22" customWidth="1"/>
+    <col min="11" max="11" width="49.85546875" style="21" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" style="21" customWidth="1"/>
+    <col min="13" max="14" width="49.85546875" style="21" customWidth="1"/>
+    <col min="15" max="15" width="0.42578125" style="22" customWidth="1"/>
+    <col min="16" max="16384" width="12.5703125" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="8"/>
       <c r="B1" s="52" t="s">
         <v>0</v>
@@ -7811,7 +7819,7 @@
       <c r="S1" s="44"/>
       <c r="T1" s="44"/>
     </row>
-    <row r="2" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>3</v>
       </c>
@@ -7857,7 +7865,7 @@
       <c r="S2" s="46"/>
       <c r="T2" s="46"/>
     </row>
-    <row r="3" spans="1:20" s="48" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" s="48" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
@@ -7887,7 +7895,7 @@
       <c r="S3" s="47"/>
       <c r="T3" s="47"/>
     </row>
-    <row r="4" spans="1:20" ht="58" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>297</v>
       </c>
@@ -7912,7 +7920,7 @@
       <c r="N4" s="2"/>
       <c r="O4" s="15"/>
     </row>
-    <row r="5" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
         <v>30</v>
       </c>
@@ -7935,7 +7943,7 @@
       <c r="N5" s="2"/>
       <c r="O5" s="15"/>
     </row>
-    <row r="6" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
         <v>30</v>
       </c>
@@ -7958,7 +7966,7 @@
       <c r="N6" s="2"/>
       <c r="O6" s="5"/>
     </row>
-    <row r="7" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
         <v>13</v>
       </c>
@@ -7983,7 +7991,7 @@
       <c r="N7" s="2"/>
       <c r="O7" s="51"/>
     </row>
-    <row r="8" spans="1:20" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="150" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -8010,7 +8018,7 @@
       <c r="N8" s="2"/>
       <c r="O8" s="5"/>
     </row>
-    <row r="9" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -8035,7 +8043,7 @@
       <c r="N9" s="2"/>
       <c r="O9" s="51"/>
     </row>
-    <row r="10" spans="1:20" ht="87" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -8060,7 +8068,7 @@
       <c r="N10" s="2"/>
       <c r="O10" s="51"/>
     </row>
-    <row r="11" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
         <v>13</v>
       </c>
@@ -8087,7 +8095,7 @@
       <c r="N11" s="2"/>
       <c r="O11" s="5"/>
     </row>
-    <row r="12" spans="1:20" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -8112,7 +8120,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="51"/>
     </row>
-    <row r="13" spans="1:20" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="105" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
@@ -8137,7 +8145,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="51"/>
     </row>
-    <row r="14" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="42"/>
       <c r="C14" s="2"/>
@@ -8159,7 +8167,7 @@
       <c r="S14" s="49"/>
       <c r="T14" s="49"/>
     </row>
-    <row r="15" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="42"/>
       <c r="C15" s="2"/>
@@ -8181,7 +8189,7 @@
       <c r="S15" s="49"/>
       <c r="T15" s="49"/>
     </row>
-    <row r="16" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="42"/>
       <c r="C16" s="2"/>
@@ -8203,7 +8211,7 @@
       <c r="S16" s="49"/>
       <c r="T16" s="49"/>
     </row>
-    <row r="17" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="42"/>
       <c r="C17" s="2"/>
@@ -8225,7 +8233,7 @@
       <c r="S17" s="49"/>
       <c r="T17" s="49"/>
     </row>
-    <row r="18" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="42"/>
       <c r="C18" s="2"/>
@@ -8247,7 +8255,7 @@
       <c r="S18" s="49"/>
       <c r="T18" s="49"/>
     </row>
-    <row r="19" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="42"/>
       <c r="C19" s="2"/>
@@ -8269,7 +8277,7 @@
       <c r="S19" s="49"/>
       <c r="T19" s="49"/>
     </row>
-    <row r="20" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="42"/>
       <c r="C20" s="2"/>
@@ -8291,7 +8299,7 @@
       <c r="S20" s="49"/>
       <c r="T20" s="49"/>
     </row>
-    <row r="21" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="42"/>
       <c r="C21" s="2"/>
@@ -8313,7 +8321,7 @@
       <c r="S21" s="49"/>
       <c r="T21" s="49"/>
     </row>
-    <row r="22" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="42"/>
       <c r="C22" s="2"/>
@@ -8335,7 +8343,7 @@
       <c r="S22" s="49"/>
       <c r="T22" s="49"/>
     </row>
-    <row r="23" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" s="50" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="42"/>
       <c r="C23" s="2"/>
@@ -8357,62 +8365,62 @@
       <c r="S23" s="49"/>
       <c r="T23" s="49"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G24" s="5"/>
       <c r="J24" s="5"/>
       <c r="O24" s="5"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G25" s="51"/>
       <c r="J25" s="51"/>
       <c r="O25" s="51"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G26" s="5"/>
       <c r="J26" s="5"/>
       <c r="O26" s="5"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G27" s="51"/>
       <c r="J27" s="51"/>
       <c r="O27" s="51"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G28" s="5"/>
       <c r="J28" s="5"/>
       <c r="O28" s="5"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G29" s="51"/>
       <c r="J29" s="51"/>
       <c r="O29" s="51"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G30" s="51"/>
       <c r="J30" s="51"/>
       <c r="O30" s="51"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G31" s="51"/>
       <c r="J31" s="51"/>
       <c r="O31" s="51"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="G32" s="5"/>
       <c r="J32" s="5"/>
       <c r="O32" s="5"/>
     </row>
-    <row r="33" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="33" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G33" s="51"/>
       <c r="J33" s="51"/>
       <c r="O33" s="51"/>
     </row>
-    <row r="34" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="34" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G34" s="5"/>
       <c r="J34" s="5"/>
       <c r="O34" s="5"/>
     </row>
-    <row r="36" spans="7:15" x14ac:dyDescent="0.35">
+    <row r="36" spans="7:15" x14ac:dyDescent="0.25">
       <c r="G36" s="5"/>
       <c r="J36" s="5"/>
       <c r="O36" s="5"/>
@@ -8445,30 +8453,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <WT_In_CfCreated xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
-    <TaxCatchAll xmlns="03dbc9e8-d730-4bfb-89ca-7dcd997030d6" xsi:nil="true"/>
-    <WT_In_ModifiedBy xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
-    <WT_In_CreatedBy xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
-    <WT_In_CfModified xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944469f-e80a-41b6-bf10-72f886351283">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101003679B83B14C47A4BAF0FE1246F72CBF3" ma:contentTypeVersion="16" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7a14ca82ab005c28680160f0e3093c13">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c944469f-e80a-41b6-bf10-72f886351283" xmlns:ns3="03dbc9e8-d730-4bfb-89ca-7dcd997030d6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4feaa6f58b74adcfb4ef3d76786e6589" ns2:_="" ns3:_="">
     <xsd:import namespace="c944469f-e80a-41b6-bf10-72f886351283"/>
@@ -8697,10 +8681,45 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <WT_In_CfCreated xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
+    <TaxCatchAll xmlns="03dbc9e8-d730-4bfb-89ca-7dcd997030d6" xsi:nil="true"/>
+    <WT_In_ModifiedBy xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
+    <WT_In_CreatedBy xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
+    <WT_In_CfModified xmlns="c944469f-e80a-41b6-bf10-72f886351283" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944469f-e80a-41b6-bf10-72f886351283">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0821E16-9F05-47DC-92FF-2B7725F57FA3}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="c944469f-e80a-41b6-bf10-72f886351283"/>
+    <ds:schemaRef ds:uri="03dbc9e8-d730-4bfb-89ca-7dcd997030d6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -8717,20 +8736,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0821E16-9F05-47DC-92FF-2B7725F57FA3}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E01F75D2-18D7-4457-A217-CD23D85DC8FD}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="c944469f-e80a-41b6-bf10-72f886351283"/>
-    <ds:schemaRef ds:uri="03dbc9e8-d730-4bfb-89ca-7dcd997030d6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>